--- a/Pinout ESP32.xlsx
+++ b/Pinout ESP32.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ba55759753d152f/Facultad/Investigación/Beca BEI/Cabina de crecimiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04138457-65BC-4C4A-8C86-922A9BAB4F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{04138457-65BC-4C4A-8C86-922A9BAB4F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3422A774-8669-4538-A5A4-143E4AD401A7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{AB8FC7C9-1F31-4D1B-ADA0-6A6C32601660}"/>
+    <workbookView xWindow="14317" yWindow="-1395" windowWidth="8805" windowHeight="10882" xr2:uid="{AB8FC7C9-1F31-4D1B-ADA0-6A6C32601660}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -527,191 +527,191 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6701214D-AB4F-43E8-93CE-1F4A53E60138}">
-  <dimension ref="B2:F22"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1"/>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1"/>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1"/>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1"/>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1"/>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1"/>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1"/>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1"/>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1"/>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1"/>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1"/>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1"/>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1"/>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1"/>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1"/>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1"/>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1"/>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="F20" t="s">
-        <v>33</v>
+      <c r="C20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D22" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Pinout ESP32.xlsx
+++ b/Pinout ESP32.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ba55759753d152f/Facultad/Investigación/Beca BEI/Cabina de crecimiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04138457-65BC-4C4A-8C86-922A9BAB4F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{04138457-65BC-4C4A-8C86-922A9BAB4F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42D47524-ACB2-460F-9516-71EFB130A74A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{AB8FC7C9-1F31-4D1B-ADA0-6A6C32601660}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>3V3</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>I00</t>
+  </si>
+  <si>
+    <t>CMD</t>
   </si>
 </sst>
 </file>
@@ -685,7 +688,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C19" s="1"/>
       <c r="F19" t="s">
